--- a/docentes/Santiago Hernández Mariana - Estadisticos 20222.xlsx
+++ b/docentes/Santiago Hernández Mariana - Estadisticos 20222.xlsx
@@ -530,16 +530,19 @@
         <v>17</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>17</v>
       </c>
-      <c r="E2">
-        <v>17</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -604,7 +607,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Santiago Hernández Mariana - Estadisticos 20222.xlsx
+++ b/docentes/Santiago Hernández Mariana - Estadisticos 20222.xlsx
@@ -598,16 +598,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
